--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/157.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/157.xlsx
@@ -426,13 +426,13 @@
         <v>-14.62957008605653</v>
       </c>
       <c r="E2">
-        <v>-15.81436164866406</v>
+        <v>-15.46909267642324</v>
       </c>
       <c r="F2">
-        <v>0.7126517846875321</v>
+        <v>0.4568916923383792</v>
       </c>
       <c r="G2">
-        <v>-11.24305079404447</v>
+        <v>-9.925850934879248</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.52575115764841</v>
       </c>
       <c r="E3">
-        <v>-15.75613452987344</v>
+        <v>-16.60988773453953</v>
       </c>
       <c r="F3">
-        <v>0.4193782461352007</v>
+        <v>0.5392347256462612</v>
       </c>
       <c r="G3">
-        <v>-11.09640355829137</v>
+        <v>-10.02258507553675</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.40506544889741</v>
       </c>
       <c r="E4">
-        <v>-16.50427466373264</v>
+        <v>-16.05199785069057</v>
       </c>
       <c r="F4">
-        <v>0.7469461951634316</v>
+        <v>0.7292125058042999</v>
       </c>
       <c r="G4">
-        <v>-10.80452600027599</v>
+        <v>-10.1237652788535</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.27939707513659</v>
       </c>
       <c r="E5">
-        <v>-17.5066071005904</v>
+        <v>-17.67211376862273</v>
       </c>
       <c r="F5">
-        <v>0.5862851657578704</v>
+        <v>0.6457909381379728</v>
       </c>
       <c r="G5">
-        <v>-10.56733203347829</v>
+        <v>-9.498611790854145</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.15655672038283</v>
       </c>
       <c r="E6">
-        <v>-17.63483537059159</v>
+        <v>-17.41404962034762</v>
       </c>
       <c r="F6">
-        <v>0.661581277570137</v>
+        <v>0.6376687957535236</v>
       </c>
       <c r="G6">
-        <v>-9.903352467394361</v>
+        <v>-9.688071001521095</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.02322546115205</v>
       </c>
       <c r="E7">
-        <v>-18.43274343379509</v>
+        <v>-18.74118232693153</v>
       </c>
       <c r="F7">
-        <v>0.5392256136048305</v>
+        <v>0.7935733395322102</v>
       </c>
       <c r="G7">
-        <v>-9.882436440677246</v>
+        <v>-8.803019825415719</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.88620657566154</v>
       </c>
       <c r="E8">
-        <v>-18.17431247912536</v>
+        <v>-19.67272112962738</v>
       </c>
       <c r="F8">
-        <v>0.9072319741355248</v>
+        <v>1.153773994026325</v>
       </c>
       <c r="G8">
-        <v>-9.144565498156789</v>
+        <v>-8.813474528228738</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.7404018552205</v>
       </c>
       <c r="E9">
-        <v>-20.0353522712136</v>
+        <v>-19.74243245850145</v>
       </c>
       <c r="F9">
-        <v>1.044325122564037</v>
+        <v>1.090556307314278</v>
       </c>
       <c r="G9">
-        <v>-8.969000647118159</v>
+        <v>-8.900849756646721</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.56815387953777</v>
       </c>
       <c r="E10">
-        <v>-19.19628490775439</v>
+        <v>-21.34298084024647</v>
       </c>
       <c r="F10">
-        <v>1.245687984306152</v>
+        <v>1.368722081174352</v>
       </c>
       <c r="G10">
-        <v>-8.350607293109997</v>
+        <v>-7.731356507807164</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.37621483084904</v>
       </c>
       <c r="E11">
-        <v>-20.86882244079934</v>
+        <v>-21.3422291135612</v>
       </c>
       <c r="F11">
-        <v>1.355445008442281</v>
+        <v>1.384845424302441</v>
       </c>
       <c r="G11">
-        <v>-8.550157046580647</v>
+        <v>-7.712880353152492</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.15093758096743</v>
       </c>
       <c r="E12">
-        <v>-21.10747754947758</v>
+        <v>-22.89369336553708</v>
       </c>
       <c r="F12">
-        <v>1.470670914171692</v>
+        <v>1.418198809408761</v>
       </c>
       <c r="G12">
-        <v>-7.826339369874394</v>
+        <v>-7.794955398162103</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.88374866551508</v>
       </c>
       <c r="E13">
-        <v>-23.02308998183225</v>
+        <v>-22.01089452858579</v>
       </c>
       <c r="F13">
-        <v>1.666834942093838</v>
+        <v>1.635345383643817</v>
       </c>
       <c r="G13">
-        <v>-7.762826553703476</v>
+        <v>-6.813875227599087</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.58846487358345</v>
       </c>
       <c r="E14">
-        <v>-24.07032676695007</v>
+        <v>-23.81332228159275</v>
       </c>
       <c r="F14">
-        <v>1.606584467418619</v>
+        <v>2.218883830341512</v>
       </c>
       <c r="G14">
-        <v>-7.282350526861353</v>
+        <v>-7.050026372551919</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.25408816820901</v>
       </c>
       <c r="E15">
-        <v>-24.28418848043631</v>
+        <v>-23.75812924038727</v>
       </c>
       <c r="F15">
-        <v>1.703616111512942</v>
+        <v>2.16509793487774</v>
       </c>
       <c r="G15">
-        <v>-7.678530132637015</v>
+        <v>-6.685998785053659</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.88766059361284</v>
       </c>
       <c r="E16">
-        <v>-23.64636197340395</v>
+        <v>-24.95646308924501</v>
       </c>
       <c r="F16">
-        <v>2.148013685562403</v>
+        <v>2.463406290504287</v>
       </c>
       <c r="G16">
-        <v>-7.11152306648942</v>
+        <v>-6.276024136015854</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.49935983225754</v>
       </c>
       <c r="E17">
-        <v>-26.29581814717562</v>
+        <v>-25.3054318247501</v>
       </c>
       <c r="F17">
-        <v>1.575948127393482</v>
+        <v>2.750561507419541</v>
       </c>
       <c r="G17">
-        <v>-5.920259670183616</v>
+        <v>-5.614206356169073</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.08414961171869</v>
       </c>
       <c r="E18">
-        <v>-26.4340135884677</v>
+        <v>-27.0193233824331</v>
       </c>
       <c r="F18">
-        <v>2.681628085628178</v>
+        <v>2.738939512758265</v>
       </c>
       <c r="G18">
-        <v>-5.614696316908885</v>
+        <v>-5.623648032047075</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.65933603209303</v>
       </c>
       <c r="E19">
-        <v>-25.36449671123214</v>
+        <v>-27.53738533738459</v>
       </c>
       <c r="F19">
-        <v>2.588231317697339</v>
+        <v>3.28534887572768</v>
       </c>
       <c r="G19">
-        <v>-5.528579095795823</v>
+        <v>-4.686151193508564</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.23371356411449</v>
       </c>
       <c r="E20">
-        <v>-28.16107847703901</v>
+        <v>-28.68031330675849</v>
       </c>
       <c r="F20">
-        <v>2.805745687059239</v>
+        <v>3.519564788664823</v>
       </c>
       <c r="G20">
-        <v>-5.702919044984923</v>
+        <v>-4.244958100035431</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.81020433130521</v>
       </c>
       <c r="E21">
-        <v>-27.9631751059558</v>
+        <v>-29.00565246489155</v>
       </c>
       <c r="F21">
-        <v>3.033767068558248</v>
+        <v>3.598374006632363</v>
       </c>
       <c r="G21">
-        <v>-5.003417325264618</v>
+        <v>-4.381842536993217</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.41327511612767</v>
       </c>
       <c r="E22">
-        <v>-27.63221158310521</v>
+        <v>-28.72174431545467</v>
       </c>
       <c r="F22">
-        <v>3.082297801218659</v>
+        <v>3.361459272696898</v>
       </c>
       <c r="G22">
-        <v>-4.241561480312139</v>
+        <v>-3.656366276971789</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.044816554679699</v>
       </c>
       <c r="E23">
-        <v>-29.2873507190127</v>
+        <v>-29.77108004827504</v>
       </c>
       <c r="F23">
-        <v>2.995247984328071</v>
+        <v>3.53031368408355</v>
       </c>
       <c r="G23">
-        <v>-4.948098109303396</v>
+        <v>-3.554656386368761</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.712459645819461</v>
       </c>
       <c r="E24">
-        <v>-29.67319255412524</v>
+        <v>-30.91138376696149</v>
       </c>
       <c r="F24">
-        <v>3.265552551535577</v>
+        <v>3.629053421762445</v>
       </c>
       <c r="G24">
-        <v>-3.976552309893481</v>
+        <v>-3.296536461217325</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.433776629780922</v>
       </c>
       <c r="E25">
-        <v>-30.19889857320168</v>
+        <v>-31.19635157931617</v>
       </c>
       <c r="F25">
-        <v>2.955940294330428</v>
+        <v>3.642615452881079</v>
       </c>
       <c r="G25">
-        <v>-3.61143886345834</v>
+        <v>-3.916618193450515</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.20267983638754</v>
       </c>
       <c r="E26">
-        <v>-30.51366148028983</v>
+        <v>-31.32681238700315</v>
       </c>
       <c r="F26">
-        <v>2.880172841465969</v>
+        <v>3.49231150111272</v>
       </c>
       <c r="G26">
-        <v>-3.042879151452828</v>
+        <v>-3.182008138286239</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.028576089898751</v>
       </c>
       <c r="E27">
-        <v>-29.36311208916102</v>
+        <v>-30.55840506772261</v>
       </c>
       <c r="F27">
-        <v>2.873226152426092</v>
+        <v>3.68427239283306</v>
       </c>
       <c r="G27">
-        <v>-3.493358325163615</v>
+        <v>-3.054545513933219</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.915988334504771</v>
       </c>
       <c r="E28">
-        <v>-31.31121632252073</v>
+        <v>-30.97240268997785</v>
       </c>
       <c r="F28">
-        <v>3.27376167249732</v>
+        <v>3.076134747741831</v>
       </c>
       <c r="G28">
-        <v>-4.311447096646154</v>
+        <v>-3.35297795211636</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.856362901412643</v>
       </c>
       <c r="E29">
-        <v>-30.35609096295594</v>
+        <v>-31.08413146493209</v>
       </c>
       <c r="F29">
-        <v>2.560500890521223</v>
+        <v>3.201057522288413</v>
       </c>
       <c r="G29">
-        <v>-3.470598324581126</v>
+        <v>-2.98327277901825</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.858846438520145</v>
       </c>
       <c r="E30">
-        <v>-30.86241964175356</v>
+        <v>-30.81038068269441</v>
       </c>
       <c r="F30">
-        <v>2.84122134945153</v>
+        <v>3.157945969177116</v>
       </c>
       <c r="G30">
-        <v>-3.881314535819727</v>
+        <v>-3.139229268827776</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.916243062350955</v>
       </c>
       <c r="E31">
-        <v>-29.34731224334826</v>
+        <v>-29.8313947935832</v>
       </c>
       <c r="F31">
-        <v>2.740448798166165</v>
+        <v>2.940282493682712</v>
       </c>
       <c r="G31">
-        <v>-3.801927653788004</v>
+        <v>-2.973665575863285</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.020223501305091</v>
       </c>
       <c r="E32">
-        <v>-29.33476384187301</v>
+        <v>-30.8209999542424</v>
       </c>
       <c r="F32">
-        <v>2.596831428073203</v>
+        <v>2.96876507846057</v>
       </c>
       <c r="G32">
-        <v>-3.507911483354251</v>
+        <v>-3.137706417879711</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.17683451493328</v>
       </c>
       <c r="E33">
-        <v>-29.23357961864562</v>
+        <v>-31.07051434359103</v>
       </c>
       <c r="F33">
-        <v>2.345942136052512</v>
+        <v>3.059877209094488</v>
       </c>
       <c r="G33">
-        <v>-2.940090023003997</v>
+        <v>-2.819394153733248</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.367797544905816</v>
       </c>
       <c r="E34">
-        <v>-30.04667844790785</v>
+        <v>-30.00323000404126</v>
       </c>
       <c r="F34">
-        <v>2.625360401425619</v>
+        <v>2.746737763488219</v>
       </c>
       <c r="G34">
-        <v>-3.586460797364539</v>
+        <v>-3.328681858403649</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.588198324138277</v>
       </c>
       <c r="E35">
-        <v>-29.55410953738253</v>
+        <v>-29.49682886965951</v>
       </c>
       <c r="F35">
-        <v>2.784095476619671</v>
+        <v>2.931972311897828</v>
       </c>
       <c r="G35">
-        <v>-4.288985045162199</v>
+        <v>-2.894983840031427</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.832925200294049</v>
       </c>
       <c r="E36">
-        <v>-28.12634960987419</v>
+        <v>-28.81847252025851</v>
       </c>
       <c r="F36">
-        <v>2.890553941757852</v>
+        <v>3.142377632208902</v>
       </c>
       <c r="G36">
-        <v>-4.429401834210386</v>
+        <v>-3.035953490184673</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.080888135279039</v>
       </c>
       <c r="E37">
-        <v>-28.16509523348381</v>
+        <v>-28.75448065405612</v>
       </c>
       <c r="F37">
-        <v>2.948246417893227</v>
+        <v>3.201090656984525</v>
       </c>
       <c r="G37">
-        <v>-3.478388038235031</v>
+        <v>-3.604370848731996</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.328483600829749</v>
       </c>
       <c r="E38">
-        <v>-26.85646134322124</v>
+        <v>-28.02763793345499</v>
       </c>
       <c r="F38">
-        <v>2.819769947188635</v>
+        <v>3.315218147537824</v>
       </c>
       <c r="G38">
-        <v>-4.540573263964652</v>
+        <v>-3.485128308952987</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.563873918246895</v>
       </c>
       <c r="E39">
-        <v>-28.45509418046101</v>
+        <v>-27.62434109527988</v>
       </c>
       <c r="F39">
-        <v>2.682532662832035</v>
+        <v>3.229165685000206</v>
       </c>
       <c r="G39">
-        <v>-4.241303257760076</v>
+        <v>-3.070045488148087</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.771899070861551</v>
       </c>
       <c r="E40">
-        <v>-26.51636841677119</v>
+        <v>-27.37170658733996</v>
       </c>
       <c r="F40">
-        <v>2.847965916845124</v>
+        <v>3.291561631248676</v>
       </c>
       <c r="G40">
-        <v>-3.447546995991181</v>
+        <v>-3.612097662020655</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.955056374997181</v>
       </c>
       <c r="E41">
-        <v>-25.66504700264721</v>
+        <v>-27.06942641885396</v>
       </c>
       <c r="F41">
-        <v>2.514629217223797</v>
+        <v>3.282000614685564</v>
       </c>
       <c r="G41">
-        <v>-4.250294699444736</v>
+        <v>-4.036734717251892</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.10194700416911</v>
       </c>
       <c r="E42">
-        <v>-25.82881926513461</v>
+        <v>-26.31185800211079</v>
       </c>
       <c r="F42">
-        <v>2.619495560213798</v>
+        <v>3.515787433308057</v>
       </c>
       <c r="G42">
-        <v>-4.954358350918158</v>
+        <v>-3.490925074192251</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.20944152768584</v>
       </c>
       <c r="E43">
-        <v>-23.9071069782916</v>
+        <v>-26.18320405555287</v>
       </c>
       <c r="F43">
-        <v>2.658730353879994</v>
+        <v>3.503993138226998</v>
       </c>
       <c r="G43">
-        <v>-5.165230170133114</v>
+        <v>-3.212577715795869</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.2880347117803</v>
       </c>
       <c r="E44">
-        <v>-25.55871390447311</v>
+        <v>-25.85116728436247</v>
       </c>
       <c r="F44">
-        <v>3.245265833841017</v>
+        <v>3.447008087853614</v>
       </c>
       <c r="G44">
-        <v>-4.547909432879677</v>
+        <v>-3.787735345061149</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.33004376929386</v>
       </c>
       <c r="E45">
-        <v>-23.96779305846839</v>
+        <v>-24.30621044953561</v>
       </c>
       <c r="F45">
-        <v>3.106350277126346</v>
+        <v>3.676841937229949</v>
       </c>
       <c r="G45">
-        <v>-4.143645474897115</v>
+        <v>-3.781448619082072</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.34552824735956</v>
       </c>
       <c r="E46">
-        <v>-23.52576871057969</v>
+        <v>-24.47987289925576</v>
       </c>
       <c r="F46">
-        <v>3.358256804317675</v>
+        <v>3.615365478798586</v>
       </c>
       <c r="G46">
-        <v>-5.017116362706122</v>
+        <v>-3.22474397065269</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.34370281450878</v>
       </c>
       <c r="E47">
-        <v>-23.36638906787973</v>
+        <v>-24.25030190943691</v>
       </c>
       <c r="F47">
-        <v>3.273118859392748</v>
+        <v>3.685175313302111</v>
       </c>
       <c r="G47">
-        <v>-4.817579851417629</v>
+        <v>-4.07189933197003</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.32122497508647</v>
       </c>
       <c r="E48">
-        <v>-22.67623604368875</v>
+        <v>-23.25627922238323</v>
       </c>
       <c r="F48">
-        <v>3.600050622255629</v>
+        <v>3.533497928379911</v>
       </c>
       <c r="G48">
-        <v>-4.840919197469491</v>
+        <v>-3.779939010316165</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.29245920255141</v>
       </c>
       <c r="E49">
-        <v>-22.78029584791101</v>
+        <v>-23.07408965610664</v>
       </c>
       <c r="F49">
-        <v>3.024780938972679</v>
+        <v>3.753908270181998</v>
       </c>
       <c r="G49">
-        <v>-4.127579397395032</v>
+        <v>-3.662825151318907</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.26013373331279</v>
       </c>
       <c r="E50">
-        <v>-21.1048963192932</v>
+        <v>-22.22704764991991</v>
       </c>
       <c r="F50">
-        <v>3.409897228208197</v>
+        <v>4.006389684350871</v>
       </c>
       <c r="G50">
-        <v>-5.866469926261537</v>
+        <v>-4.196663861708544</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.22248636123316</v>
       </c>
       <c r="E51">
-        <v>-21.72801434274864</v>
+        <v>-22.17411884571826</v>
       </c>
       <c r="F51">
-        <v>3.105203816640871</v>
+        <v>3.514760257728586</v>
       </c>
       <c r="G51">
-        <v>-5.728145401994169</v>
+        <v>-4.245815531330103</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.19355222572633</v>
       </c>
       <c r="E52">
-        <v>-20.14957849958308</v>
+        <v>-21.91419349462599</v>
       </c>
       <c r="F52">
-        <v>3.087490008099407</v>
+        <v>3.956432503022838</v>
       </c>
       <c r="G52">
-        <v>-4.259358973131261</v>
+        <v>-4.157711982893479</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.16600587634582</v>
       </c>
       <c r="E53">
-        <v>-19.64186410773911</v>
+        <v>-20.78186215443004</v>
       </c>
       <c r="F53">
-        <v>3.626772097935135</v>
+        <v>3.824688951281604</v>
       </c>
       <c r="G53">
-        <v>-5.095374348708953</v>
+        <v>-4.509656079173398</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.13972185705818</v>
       </c>
       <c r="E54">
-        <v>-19.43454151071995</v>
+        <v>-21.07374041812043</v>
       </c>
       <c r="F54">
-        <v>3.150126180894689</v>
+        <v>3.560731335114347</v>
       </c>
       <c r="G54">
-        <v>-5.411415578615477</v>
+        <v>-4.924239007601869</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.1233642573507</v>
       </c>
       <c r="E55">
-        <v>-19.79520729458685</v>
+        <v>-20.3700427281725</v>
       </c>
       <c r="F55">
-        <v>3.409522806142131</v>
+        <v>3.799195116093047</v>
       </c>
       <c r="G55">
-        <v>-5.397213338252004</v>
+        <v>-4.353643310089704</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.10481847621597</v>
       </c>
       <c r="E56">
-        <v>-18.75697311579628</v>
+        <v>-19.86717833199075</v>
       </c>
       <c r="F56">
-        <v>2.936703946502619</v>
+        <v>3.666747452059434</v>
       </c>
       <c r="G56">
-        <v>-6.425832942758954</v>
+        <v>-5.532296838436425</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.09016112920742</v>
       </c>
       <c r="E57">
-        <v>-18.60987922307913</v>
+        <v>-19.93769120076418</v>
       </c>
       <c r="F57">
-        <v>3.469451874265065</v>
+        <v>3.838005785649009</v>
       </c>
       <c r="G57">
-        <v>-5.309046889450133</v>
+        <v>-5.289647092590005</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.08170305685181</v>
       </c>
       <c r="E58">
-        <v>-19.00154241152853</v>
+        <v>-19.84587186178466</v>
       </c>
       <c r="F58">
-        <v>3.086986360718505</v>
+        <v>3.688773741299873</v>
       </c>
       <c r="G58">
-        <v>-5.575443178449746</v>
+        <v>-4.94539670414335</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.06990962763193</v>
       </c>
       <c r="E59">
-        <v>-18.39282040694347</v>
+        <v>-18.5927978191222</v>
       </c>
       <c r="F59">
-        <v>3.174907620116838</v>
+        <v>3.987766328401132</v>
       </c>
       <c r="G59">
-        <v>-6.055975484566038</v>
+        <v>-5.043984750302847</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.06300587367431</v>
       </c>
       <c r="E60">
-        <v>-17.84073602677235</v>
+        <v>-19.35860805855933</v>
       </c>
       <c r="F60">
-        <v>3.173610396764055</v>
+        <v>3.720495242622677</v>
       </c>
       <c r="G60">
-        <v>-6.477477453171585</v>
+        <v>-5.048953879157293</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.05461422537699</v>
       </c>
       <c r="E61">
-        <v>-17.25916222386327</v>
+        <v>-17.99870731405592</v>
       </c>
       <c r="F61">
-        <v>2.83227332476649</v>
+        <v>3.90209160139919</v>
       </c>
       <c r="G61">
-        <v>-6.104858999998916</v>
+        <v>-5.21680846963496</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.03654116068141</v>
       </c>
       <c r="E62">
-        <v>-17.68438593318352</v>
+        <v>-18.68356655213194</v>
       </c>
       <c r="F62">
-        <v>3.236408929570285</v>
+        <v>3.789074123165642</v>
       </c>
       <c r="G62">
-        <v>-6.751299295815783</v>
+        <v>-5.643941676202807</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.01635739186698</v>
       </c>
       <c r="E63">
-        <v>-18.07044287081143</v>
+        <v>-18.05390941220942</v>
       </c>
       <c r="F63">
-        <v>2.918484833845446</v>
+        <v>3.639789063302727</v>
       </c>
       <c r="G63">
-        <v>-6.544883470896686</v>
+        <v>-5.138994096734391</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.980665366190911</v>
       </c>
       <c r="E64">
-        <v>-17.24852483841926</v>
+        <v>-16.7049222900645</v>
       </c>
       <c r="F64">
-        <v>3.507941137268741</v>
+        <v>3.773063438004334</v>
       </c>
       <c r="G64">
-        <v>-6.774198339310922</v>
+        <v>-5.391403330830583</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.928587978811622</v>
       </c>
       <c r="E65">
-        <v>-16.84550876563263</v>
+        <v>-17.8814470081013</v>
       </c>
       <c r="F65">
-        <v>3.282968147812034</v>
+        <v>3.845048565307611</v>
       </c>
       <c r="G65">
-        <v>-6.798752655575696</v>
+        <v>-6.209578176497143</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.865290860981339</v>
       </c>
       <c r="E66">
-        <v>-16.05134575043347</v>
+        <v>-18.38237774588178</v>
       </c>
       <c r="F66">
-        <v>3.136890526532758</v>
+        <v>3.978523404920695</v>
       </c>
       <c r="G66">
-        <v>-7.447828145641823</v>
+        <v>-4.990327428202339</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.779721352184076</v>
       </c>
       <c r="E67">
-        <v>-15.4445075910356</v>
+        <v>-17.13515449163723</v>
       </c>
       <c r="F67">
-        <v>3.301394352319906</v>
+        <v>3.668598024837288</v>
       </c>
       <c r="G67">
-        <v>-7.047708990674429</v>
+        <v>-5.97870073058837</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.676777730432439</v>
       </c>
       <c r="E68">
-        <v>-15.98572816206232</v>
+        <v>-17.05193019632426</v>
       </c>
       <c r="F68">
-        <v>3.356846922998111</v>
+        <v>3.627618689420796</v>
       </c>
       <c r="G68">
-        <v>-7.038985703178449</v>
+        <v>-5.535306124331623</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.555891063754135</v>
       </c>
       <c r="E69">
-        <v>-15.42770695246714</v>
+        <v>-17.55746186369654</v>
       </c>
       <c r="F69">
-        <v>2.978352602780572</v>
+        <v>3.265201323756791</v>
       </c>
       <c r="G69">
-        <v>-7.170113101443442</v>
+        <v>-5.844325687149352</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.407883874438312</v>
       </c>
       <c r="E70">
-        <v>-16.1055017710912</v>
+        <v>-17.35617119405559</v>
       </c>
       <c r="F70">
-        <v>2.731386458779538</v>
+        <v>3.749721701328249</v>
       </c>
       <c r="G70">
-        <v>-6.623062003806575</v>
+        <v>-5.851843936069037</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.239959134317973</v>
       </c>
       <c r="E71">
-        <v>-16.71116252724707</v>
+        <v>-16.96670431549991</v>
       </c>
       <c r="F71">
-        <v>2.469431834992251</v>
+        <v>3.363631252027039</v>
       </c>
       <c r="G71">
-        <v>-7.137106962416908</v>
+        <v>-6.249999937531643</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.046919651145783</v>
       </c>
       <c r="E72">
-        <v>-16.31317306060895</v>
+        <v>-16.34364969068058</v>
       </c>
       <c r="F72">
-        <v>2.62927857924086</v>
+        <v>3.070433923275765</v>
       </c>
       <c r="G72">
-        <v>-6.401632854866881</v>
+        <v>-6.467992740201573</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.824009258351204</v>
       </c>
       <c r="E73">
-        <v>-16.58667477677621</v>
+        <v>-16.83237619101038</v>
       </c>
       <c r="F73">
-        <v>2.837392635315791</v>
+        <v>3.028704086992337</v>
       </c>
       <c r="G73">
-        <v>-6.631384715292302</v>
+        <v>-6.093662734985101</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.582278281495608</v>
       </c>
       <c r="E74">
-        <v>-16.75205464753633</v>
+        <v>-16.68334411141795</v>
       </c>
       <c r="F74">
-        <v>2.529539830474189</v>
+        <v>3.093654718311041</v>
       </c>
       <c r="G74">
-        <v>-5.964389242222101</v>
+        <v>-6.05055943206379</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.316446753773432</v>
       </c>
       <c r="E75">
-        <v>-16.81800734298404</v>
+        <v>-17.33178988999829</v>
       </c>
       <c r="F75">
-        <v>2.520563641297453</v>
+        <v>2.953866062353819</v>
       </c>
       <c r="G75">
-        <v>-5.897294415777691</v>
+        <v>-5.838674585913816</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.032944273723357</v>
       </c>
       <c r="E76">
-        <v>-15.92050002245584</v>
+        <v>-17.09429859914003</v>
       </c>
       <c r="F76">
-        <v>2.56204165389043</v>
+        <v>3.100016579964541</v>
       </c>
       <c r="G76">
-        <v>-6.586414264686843</v>
+        <v>-4.867307555963022</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.743483556997126</v>
       </c>
       <c r="E77">
-        <v>-18.04690839139356</v>
+        <v>-18.15047459194898</v>
       </c>
       <c r="F77">
-        <v>2.301069473842862</v>
+        <v>2.709189525854123</v>
       </c>
       <c r="G77">
-        <v>-5.759009618056795</v>
+        <v>-5.35103453852471</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.446693839332517</v>
       </c>
       <c r="E78">
-        <v>-17.42095101473531</v>
+        <v>-18.33194413085836</v>
       </c>
       <c r="F78">
-        <v>2.006021572313735</v>
+        <v>2.833756102417501</v>
       </c>
       <c r="G78">
-        <v>-5.501349858735318</v>
+        <v>-5.340367960797178</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.15469652763912</v>
       </c>
       <c r="E79">
-        <v>-16.49832877736057</v>
+        <v>-18.39976255759723</v>
       </c>
       <c r="F79">
-        <v>2.018563054792119</v>
+        <v>2.634687818381141</v>
       </c>
       <c r="G79">
-        <v>-5.930515740264278</v>
+        <v>-4.6915242089188</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.873249805354219</v>
       </c>
       <c r="E80">
-        <v>-19.42943339203929</v>
+        <v>-19.3131285941003</v>
       </c>
       <c r="F80">
-        <v>2.106020428444885</v>
+        <v>2.722683630845727</v>
       </c>
       <c r="G80">
-        <v>-5.098641857156214</v>
+        <v>-5.716356549328824</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.601028234197557</v>
       </c>
       <c r="E81">
-        <v>-18.68784143159518</v>
+        <v>-20.28634294308873</v>
       </c>
       <c r="F81">
-        <v>2.03177220139716</v>
+        <v>2.573544363645704</v>
       </c>
       <c r="G81">
-        <v>-5.746783773380266</v>
+        <v>-4.533664155424193</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.350747777927228</v>
       </c>
       <c r="E82">
-        <v>-20.34671203008499</v>
+        <v>-19.95719533831522</v>
       </c>
       <c r="F82">
-        <v>2.383376058985021</v>
+        <v>2.458803881214333</v>
       </c>
       <c r="G82">
-        <v>-5.870243948176307</v>
+        <v>-4.277447793957839</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.12131790241942</v>
       </c>
       <c r="E83">
-        <v>-21.53823505403519</v>
+        <v>-21.61796336741424</v>
       </c>
       <c r="F83">
-        <v>1.691063031890918</v>
+        <v>2.44687539061402</v>
       </c>
       <c r="G83">
-        <v>-4.983544120392373</v>
+        <v>-4.133170908810861</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.913282451658867</v>
       </c>
       <c r="E84">
-        <v>-22.34468834769117</v>
+        <v>-22.36004440305118</v>
       </c>
       <c r="F84">
-        <v>2.207510345901075</v>
+        <v>2.371384612462096</v>
       </c>
       <c r="G84">
-        <v>-4.954990665116158</v>
+        <v>-3.542162387503551</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.737741090177113</v>
       </c>
       <c r="E85">
-        <v>-22.49012481892151</v>
+        <v>-23.0682841524288</v>
       </c>
       <c r="F85">
-        <v>1.742512931278795</v>
+        <v>2.099431594123018</v>
       </c>
       <c r="G85">
-        <v>-5.345750907844033</v>
+        <v>-4.016808543651019</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.589289924389234</v>
       </c>
       <c r="E86">
-        <v>-23.29777815818952</v>
+        <v>-24.13786442830046</v>
       </c>
       <c r="F86">
-        <v>1.444310606679807</v>
+        <v>2.003110689260297</v>
       </c>
       <c r="G86">
-        <v>-4.118101305516099</v>
+        <v>-3.508308748818964</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.474356566395335</v>
       </c>
       <c r="E87">
-        <v>-25.87459760887815</v>
+        <v>-24.61087712382366</v>
       </c>
       <c r="F87">
-        <v>1.168764130547385</v>
+        <v>1.915490955596582</v>
       </c>
       <c r="G87">
-        <v>-4.024369829662714</v>
+        <v>-3.481632372863517</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.39935346699882</v>
       </c>
       <c r="E88">
-        <v>-26.57384833735055</v>
+        <v>-26.78519674776253</v>
       </c>
       <c r="F88">
-        <v>1.091600050241805</v>
+        <v>2.202957638655289</v>
       </c>
       <c r="G88">
-        <v>-4.660686477220489</v>
+        <v>-2.535915449750995</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.361721571138945</v>
       </c>
       <c r="E89">
-        <v>-28.09749417349731</v>
+        <v>-27.0785422370314</v>
       </c>
       <c r="F89">
-        <v>1.530253724720255</v>
+        <v>1.704805647103362</v>
       </c>
       <c r="G89">
-        <v>-4.024091743837415</v>
+        <v>-2.583375430601987</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.374084834561942</v>
       </c>
       <c r="E90">
-        <v>-29.53214190997132</v>
+        <v>-29.05023076302306</v>
       </c>
       <c r="F90">
-        <v>1.264980661117353</v>
+        <v>1.587245402032861</v>
       </c>
       <c r="G90">
-        <v>-3.367385446303268</v>
+        <v>-2.710424236762597</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.438865462232846</v>
       </c>
       <c r="E91">
-        <v>-29.63502883942559</v>
+        <v>-29.82324127613239</v>
       </c>
       <c r="F91">
-        <v>1.07048330840964</v>
+        <v>1.423657750593209</v>
       </c>
       <c r="G91">
-        <v>-2.980485299674184</v>
+        <v>-3.11386386890588</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.558254662900781</v>
       </c>
       <c r="E92">
-        <v>-31.62776797684191</v>
+        <v>-31.59136583853125</v>
       </c>
       <c r="F92">
-        <v>0.8057884452538917</v>
+        <v>1.183532264604494</v>
       </c>
       <c r="G92">
-        <v>-3.188692129730027</v>
+        <v>-3.662308706214781</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.745918314342628</v>
       </c>
       <c r="E93">
-        <v>-32.64520061027824</v>
+        <v>-33.9104924758134</v>
       </c>
       <c r="F93">
-        <v>0.6522165840814886</v>
+        <v>0.9745119745909007</v>
       </c>
       <c r="G93">
-        <v>-2.666642272005736</v>
+        <v>-3.313062704549367</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.99542323251358</v>
       </c>
       <c r="E94">
-        <v>-35.59050425520802</v>
+        <v>-35.35024606673107</v>
       </c>
       <c r="F94">
-        <v>0.1028151580531613</v>
+        <v>0.6597920039800901</v>
       </c>
       <c r="G94">
-        <v>-4.16724304350104</v>
+        <v>-3.170967468912769</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.309671311954776</v>
       </c>
       <c r="E95">
-        <v>-36.75872601615175</v>
+        <v>-37.55733599282645</v>
       </c>
       <c r="F95">
-        <v>0.2606406858389399</v>
+        <v>0.4143177496714986</v>
       </c>
       <c r="G95">
-        <v>-3.902065035259879</v>
+        <v>-3.378985597872874</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.693041407745128</v>
       </c>
       <c r="E96">
-        <v>-39.53106459635856</v>
+        <v>-38.55791138176923</v>
       </c>
       <c r="F96">
-        <v>0.03369204012655654</v>
+        <v>-0.1065389640237606</v>
       </c>
       <c r="G96">
-        <v>-3.817768614193417</v>
+        <v>-3.169706151062307</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.123851039174152</v>
       </c>
       <c r="E97">
-        <v>-41.84687186219309</v>
+        <v>-41.10358851670711</v>
       </c>
       <c r="F97">
-        <v>-0.0959325477983157</v>
+        <v>-0.2739047991875811</v>
       </c>
       <c r="G97">
-        <v>-4.035797832864278</v>
+        <v>-3.202172671165939</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.606440499037093</v>
       </c>
       <c r="E98">
-        <v>-43.6738914932987</v>
+        <v>-42.56800644130755</v>
       </c>
       <c r="F98">
-        <v>-0.8038279941064808</v>
+        <v>-0.412012697684523</v>
       </c>
       <c r="G98">
-        <v>-4.186997068733872</v>
+        <v>-3.58032304593473</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.10904458072272</v>
       </c>
       <c r="E99">
-        <v>-45.13586404193501</v>
+        <v>-45.25060651634136</v>
       </c>
       <c r="F99">
-        <v>-0.863194600762913</v>
+        <v>-0.5898590372285629</v>
       </c>
       <c r="G99">
-        <v>-4.069267448266309</v>
+        <v>-3.483986170741939</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.63197673384337</v>
       </c>
       <c r="E100">
-        <v>-48.20342063541285</v>
+        <v>-47.17216709930511</v>
       </c>
       <c r="F100">
-        <v>-0.9159458653405883</v>
+        <v>-0.9684212835731314</v>
       </c>
       <c r="G100">
-        <v>-5.735584197820912</v>
+        <v>-3.594955657218309</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.123315340311171</v>
       </c>
       <c r="E101">
-        <v>-48.68118143593308</v>
+        <v>-49.92822581545434</v>
       </c>
       <c r="F101">
-        <v>-1.194737056589776</v>
+        <v>-0.8042670288299646</v>
       </c>
       <c r="G101">
-        <v>-4.171414330880522</v>
+        <v>-3.892583632835406</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.621502704804142</v>
       </c>
       <c r="E102">
-        <v>-50.45845804430145</v>
+        <v>-51.61333552446309</v>
       </c>
       <c r="F102">
-        <v>-1.707375537281861</v>
+        <v>-1.097227444504038</v>
       </c>
       <c r="G102">
-        <v>-4.743224998605599</v>
+        <v>-4.843941725546846</v>
       </c>
     </row>
   </sheetData>
